--- a/Tests Data/Renogy RNG-50DB-H – 50 W/Single-diode model/STC/Single-diode emulator - Renogy RNG-50DB-H – 50 W (STC).xlsx
+++ b/Tests Data/Renogy RNG-50DB-H – 50 W/Single-diode model/STC/Single-diode emulator - Renogy RNG-50DB-H – 50 W (STC).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\Test Data - new\Renogy RNG-50DB-H – 50 W\Single-diode model\STC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Desktop\Stage_GeePs\PV-emulator\Tests Data\Renogy RNG-50DB-H – 50 W\Single-diode model\STC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B504B214-EF34-456B-958B-974B9AB567CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86945922-A918-4907-8AA9-A10DE175FAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
+    <workbookView xWindow="32535" yWindow="0" windowWidth="16860" windowHeight="15585" xr2:uid="{217CCB4B-160F-4504-987F-9C10DFEEC66E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -537,57 +537,57 @@
         <v>60</v>
       </c>
       <c r="B2">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="C2">
         <f>A2*B2</f>
-        <v>19.2</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D2">
-        <v>5.0599999999999996</v>
+        <v>5.95</v>
       </c>
       <c r="E2">
-        <v>2.44</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F2">
         <f>D2*E2</f>
-        <v>12.346399999999999</v>
+        <v>12.1975</v>
       </c>
       <c r="G2">
         <f>D2/E2</f>
-        <v>2.0737704918032787</v>
+        <v>2.9024390243902443</v>
       </c>
       <c r="H2">
-        <v>22.825958</v>
+        <v>23.424229</v>
       </c>
       <c r="I2">
-        <v>12.842241</v>
+        <v>11.58681</v>
       </c>
       <c r="J2">
-        <v>5.1794130000000003</v>
+        <v>5.8945309999999997</v>
       </c>
       <c r="K2">
-        <v>2.9140190000000001</v>
+        <v>2.915734</v>
       </c>
       <c r="L2">
         <f>J2/K2</f>
-        <v>1.7774122268935104</v>
+        <v>2.0216285161815173</v>
       </c>
       <c r="M2">
         <f>ABS(J2-D2)/D2*100</f>
-        <v>2.359940711462464</v>
+        <v>0.93225210084034349</v>
       </c>
       <c r="N2">
         <f>ABS(K2-E2)/E2*100</f>
-        <v>19.427008196721321</v>
+        <v>42.230926829268306</v>
       </c>
       <c r="O2">
         <f t="shared" ref="O2:O18" si="0">(ABS(L2-G2)/G2)*100</f>
-        <v>14.290793801973015</v>
+        <v>30.347252803830081</v>
       </c>
       <c r="P2">
         <f t="shared" ref="P2:P18" si="1">(F2/C2)*100</f>
-        <v>64.30416666666666</v>
+        <v>65.577956989247312</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -595,57 +595,57 @@
         <v>60</v>
       </c>
       <c r="B3">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="C3">
         <f>A3*B3</f>
-        <v>39.6</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="D3">
-        <v>11.15</v>
+        <v>11.9</v>
       </c>
       <c r="E3">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="F3">
         <f>D3*E3</f>
-        <v>32.223500000000001</v>
+        <v>33.082000000000001</v>
       </c>
       <c r="G3">
         <f>D3/E3</f>
-        <v>3.8581314878892732</v>
+        <v>4.2805755395683454</v>
       </c>
       <c r="H3">
-        <v>22.825714000000001</v>
+        <v>23.72953</v>
       </c>
       <c r="I3">
-        <v>5.812697</v>
+        <v>5.6934110000000002</v>
       </c>
       <c r="J3">
-        <v>11.411573000000001</v>
+        <v>12.125871</v>
       </c>
       <c r="K3">
-        <v>2.9060220000000001</v>
+        <v>2.9093520000000002</v>
       </c>
       <c r="L3">
         <f>J3/K3</f>
-        <v>3.9268708220378237</v>
+        <v>4.1678940877556236</v>
       </c>
       <c r="M3">
         <f t="shared" ref="M3:M18" si="2">ABS(J3-D3)/D3*100</f>
-        <v>2.3459461883408097</v>
+        <v>1.8980756302520982</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N18" si="3">ABS(K3-E3)/E3*100</f>
-        <v>0.55439446366781941</v>
+        <v>4.6529496402877832</v>
       </c>
       <c r="O3">
         <f t="shared" si="0"/>
-        <v>1.7816742214287977</v>
+        <v>2.6323902188182045</v>
       </c>
       <c r="P3">
         <f t="shared" si="1"/>
-        <v>81.37247474747474</v>
+        <v>82.293532338308452</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -653,57 +653,57 @@
         <v>60</v>
       </c>
       <c r="B4">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C16" si="4">A2*B4</f>
-        <v>49.8</v>
+        <v>46.2</v>
       </c>
       <c r="D4">
-        <v>14.96</v>
+        <v>13.61</v>
       </c>
       <c r="E4">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="F4">
         <f>D4*E4</f>
-        <v>42.486400000000003</v>
+        <v>38.924599999999998</v>
       </c>
       <c r="G4">
         <f>D4/E4</f>
-        <v>5.2676056338028179</v>
+        <v>4.7587412587412583</v>
       </c>
       <c r="H4">
-        <v>22.534130000000001</v>
+        <v>23.426763999999999</v>
       </c>
       <c r="I4">
-        <v>4.2845079999999998</v>
+        <v>4.9220090000000001</v>
       </c>
       <c r="J4">
-        <v>15.187758000000001</v>
+        <v>13.816704</v>
       </c>
       <c r="K4">
-        <v>2.8877120000000001</v>
+        <v>2.902917</v>
       </c>
       <c r="L4">
         <f>J4/K4</f>
-        <v>5.2594434625059563</v>
+        <v>4.7595931953962172</v>
       </c>
       <c r="M4">
         <f t="shared" si="2"/>
-        <v>1.5224465240641689</v>
+        <v>1.5187656135194727</v>
       </c>
       <c r="N4">
         <f t="shared" si="3"/>
-        <v>1.6800000000000073</v>
+        <v>1.5005944055944089</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>0.15495031071582152</v>
+        <v>1.7902563065263388E-2</v>
       </c>
       <c r="P4">
         <f t="shared" si="1"/>
-        <v>85.314056224899616</v>
+        <v>84.252380952380946</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -718,50 +718,50 @@
         <v>52.2</v>
       </c>
       <c r="D5">
-        <v>15.97</v>
+        <v>15.98</v>
       </c>
       <c r="E5" s="3">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="F5">
         <f>D5*E5</f>
-        <v>45.354799999999997</v>
+        <v>45.542999999999999</v>
       </c>
       <c r="G5">
         <f>D5/E5</f>
-        <v>5.6232394366197189</v>
+        <v>5.6070175438596488</v>
       </c>
       <c r="H5">
-        <v>22.533111999999999</v>
+        <v>23.424603000000001</v>
       </c>
       <c r="I5">
-        <v>4.0061090000000004</v>
+        <v>4.1703530000000004</v>
       </c>
       <c r="J5">
-        <v>16.149439000000001</v>
+        <v>16.145973000000001</v>
       </c>
       <c r="K5">
-        <v>2.8711709999999999</v>
+        <v>2.8745159999999998</v>
       </c>
       <c r="L5">
         <f t="shared" ref="L5:L15" si="5">J5/K5</f>
-        <v>5.624687279162405</v>
+        <v>5.6169362076954874</v>
       </c>
       <c r="M5">
         <f t="shared" si="2"/>
-        <v>1.1236005009392633</v>
+        <v>1.0386295369211578</v>
       </c>
       <c r="N5">
         <f t="shared" si="3"/>
-        <v>1.0975704225352134</v>
+        <v>0.86021052631578099</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>2.5747481660791188E-2</v>
+        <v>0.17689732122740959</v>
       </c>
       <c r="P5">
         <f t="shared" si="1"/>
-        <v>86.886590038314168</v>
+        <v>87.247126436781613</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -769,57 +769,57 @@
         <v>60</v>
       </c>
       <c r="B6">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="C6">
         <f t="shared" si="4"/>
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>16.440000000000001</v>
+        <v>16.55</v>
       </c>
       <c r="E6" s="3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="F6">
         <f>D6*E6</f>
-        <v>46.360799999999998</v>
+        <v>47.002000000000002</v>
       </c>
       <c r="G6">
         <f>D6/E6</f>
-        <v>5.8297872340425538</v>
+        <v>5.8274647887323949</v>
       </c>
       <c r="H6">
-        <v>22.533306</v>
+        <v>23.426394999999999</v>
       </c>
       <c r="I6">
-        <v>3.8730920000000002</v>
+        <v>4.0028629999999996</v>
       </c>
       <c r="J6">
-        <v>16.624013999999999</v>
+        <v>16.715783999999999</v>
       </c>
       <c r="K6">
-        <v>2.8573849999999998</v>
+        <v>2.8562219999999998</v>
       </c>
       <c r="L6">
         <f t="shared" ref="L6" si="6">J6/K6</f>
-        <v>5.81791183197224</v>
+        <v>5.8524106319466762</v>
       </c>
       <c r="M6">
         <f t="shared" si="2"/>
-        <v>1.1193065693430515</v>
+        <v>1.0017160120845836</v>
       </c>
       <c r="N6">
         <f t="shared" si="3"/>
-        <v>1.3257092198581562</v>
+        <v>0.57119718309859013</v>
       </c>
       <c r="O6">
         <f t="shared" si="0"/>
-        <v>0.20370215230100294</v>
+        <v>0.42807368416047636</v>
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>86.817977528089884</v>
+        <v>87.040740740740745</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -827,57 +827,57 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="C7">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="D7">
-        <v>17.09</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="E7">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="F7">
         <f t="shared" ref="F7" si="7">D7*E7</f>
-        <v>46.826600000000006</v>
+        <v>47.823999999999991</v>
       </c>
       <c r="G7">
         <f t="shared" ref="G7" si="8">D7/E7</f>
-        <v>6.2372262773722627</v>
+        <v>6.1</v>
       </c>
       <c r="H7">
-        <v>22.532803000000001</v>
+        <v>23.423584000000002</v>
       </c>
       <c r="I7">
-        <v>3.6949920000000001</v>
+        <v>3.8488560000000001</v>
       </c>
       <c r="J7">
-        <v>17.250757</v>
+        <v>17.231912999999999</v>
       </c>
       <c r="K7">
-        <v>2.828827</v>
+        <v>2.8314689999999998</v>
       </c>
       <c r="L7">
         <f t="shared" si="5"/>
-        <v>6.0982014806843967</v>
+        <v>6.0858561403992066</v>
       </c>
       <c r="M7">
         <f t="shared" si="2"/>
-        <v>0.94064950263312042</v>
+        <v>0.88942037470726243</v>
       </c>
       <c r="N7">
         <f t="shared" si="3"/>
-        <v>3.2418613138686041</v>
+        <v>1.1238928571428561</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>2.2289522698932278</v>
+        <v>0.23186655083267224</v>
       </c>
       <c r="P7">
         <f t="shared" si="1"/>
-        <v>86.715925925925944</v>
+        <v>87.589743589743577</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -892,50 +892,50 @@
         <v>55.2</v>
       </c>
       <c r="D8">
-        <v>17.350000000000001</v>
+        <v>17.510000000000002</v>
       </c>
       <c r="E8">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="F8">
         <f>D8*E8</f>
-        <v>47.539000000000009</v>
+        <v>48.327600000000004</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G12" si="9">D8/E8</f>
-        <v>6.3321167883211675</v>
+        <v>6.3442028985507255</v>
       </c>
       <c r="H8">
-        <v>22.534594999999999</v>
+        <v>23.424973000000001</v>
       </c>
       <c r="I8">
-        <v>3.6172719999999998</v>
+        <v>3.7152159999999999</v>
       </c>
       <c r="J8">
-        <v>17.517166</v>
+        <v>17.664825</v>
       </c>
       <c r="K8">
-        <v>2.8118699999999999</v>
+        <v>2.8016529999999999</v>
       </c>
       <c r="L8">
         <f t="shared" si="5"/>
-        <v>6.2297211464256881</v>
+        <v>6.3051437847584983</v>
       </c>
       <c r="M8">
         <f t="shared" si="2"/>
-        <v>0.96349279538903831</v>
+        <v>0.8842090234151847</v>
       </c>
       <c r="N8">
         <f t="shared" si="3"/>
-        <v>2.6229927007299145</v>
+        <v>1.5091666666666728</v>
       </c>
       <c r="O8">
         <f t="shared" si="0"/>
-        <v>1.6170839123551222</v>
+        <v>0.61566621397228394</v>
       </c>
       <c r="P8">
         <f t="shared" si="1"/>
-        <v>86.121376811594217</v>
+        <v>87.550000000000011</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -943,57 +943,57 @@
         <v>60</v>
       </c>
       <c r="B9">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="C9">
         <f t="shared" si="4"/>
-        <v>57</v>
+        <v>55.800000000000004</v>
       </c>
       <c r="D9">
-        <v>17.760000000000002</v>
+        <v>18.05</v>
       </c>
       <c r="E9">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="F9">
         <f>D9*E9</f>
-        <v>49.728000000000002</v>
+        <v>48.915500000000002</v>
       </c>
       <c r="G9">
         <f t="shared" ref="G9" si="10">D9/E9</f>
-        <v>6.3428571428571434</v>
+        <v>6.6605166051660518</v>
       </c>
       <c r="H9">
-        <v>22.531389000000001</v>
+        <v>23.426898999999999</v>
       </c>
       <c r="I9">
-        <v>3.4912100000000001</v>
+        <v>3.5455830000000002</v>
       </c>
       <c r="J9">
-        <v>17.929047000000001</v>
+        <v>18.180427999999999</v>
       </c>
       <c r="K9">
-        <v>2.7780830000000001</v>
+        <v>2.751547</v>
       </c>
       <c r="L9">
         <f t="shared" ref="L9" si="11">J9/K9</f>
-        <v>6.4537477821936928</v>
+        <v>6.6073477938047214</v>
       </c>
       <c r="M9">
         <f t="shared" si="2"/>
-        <v>0.95184121621621087</v>
+        <v>0.72259279778392482</v>
       </c>
       <c r="N9">
         <f t="shared" si="3"/>
-        <v>0.78274999999999095</v>
+        <v>1.5330996309963101</v>
       </c>
       <c r="O9">
         <f t="shared" si="0"/>
-        <v>1.7482758453960492</v>
+        <v>0.79826858054961503</v>
       </c>
       <c r="P9">
         <f t="shared" si="1"/>
-        <v>87.242105263157896</v>
+        <v>87.662186379928315</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1008,50 +1008,50 @@
         <v>55.2</v>
       </c>
       <c r="D10">
-        <v>18.34</v>
+        <v>18.63</v>
       </c>
       <c r="E10">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="F10">
         <f>D10*E10</f>
-        <v>48.4176</v>
+        <v>48.624299999999998</v>
       </c>
       <c r="G10">
         <f>D10/E10</f>
-        <v>6.9469696969696964</v>
+        <v>7.1379310344827589</v>
       </c>
       <c r="H10">
-        <v>22.532783999999999</v>
+        <v>23.427966999999999</v>
       </c>
       <c r="I10">
-        <v>3.3135530000000002</v>
+        <v>3.3445809999999998</v>
       </c>
       <c r="J10">
-        <v>18.462983999999999</v>
+        <v>18.727219000000002</v>
       </c>
       <c r="K10">
-        <v>2.7150699999999999</v>
+        <v>2.6735009999999999</v>
       </c>
       <c r="L10">
         <f t="shared" si="5"/>
-        <v>6.8001871038315773</v>
+        <v>7.0047548140060547</v>
       </c>
       <c r="M10">
         <f t="shared" si="2"/>
-        <v>0.67057797164666777</v>
+        <v>0.5218411164788116</v>
       </c>
       <c r="N10">
         <f t="shared" si="3"/>
-        <v>2.8435606060605965</v>
+        <v>2.4329885057471277</v>
       </c>
       <c r="O10">
         <f t="shared" si="0"/>
-        <v>2.1129010135476243</v>
+        <v>1.8657538134417495</v>
       </c>
       <c r="P10">
         <f t="shared" si="1"/>
-        <v>87.713043478260872</v>
+        <v>88.087499999999991</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1059,57 +1059,57 @@
         <v>60</v>
       </c>
       <c r="B11">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="C11">
         <f t="shared" si="4"/>
-        <v>55.800000000000004</v>
+        <v>54.6</v>
       </c>
       <c r="D11">
-        <v>18.579999999999998</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="E11">
-        <v>2.62</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="F11">
         <f>D11*E11</f>
-        <v>48.679600000000001</v>
+        <v>47.941000000000003</v>
       </c>
       <c r="G11">
         <f t="shared" si="9"/>
-        <v>7.0916030534351133</v>
+        <v>7.609561752988049</v>
       </c>
       <c r="H11">
-        <v>22.532482000000002</v>
+        <v>23.427264999999998</v>
       </c>
       <c r="I11">
-        <v>3.2184379999999999</v>
+        <v>3.1492900000000001</v>
       </c>
       <c r="J11">
-        <v>18.722518999999998</v>
+        <v>19.188766000000001</v>
       </c>
       <c r="K11">
-        <v>2.6742400000000002</v>
+        <v>2.5795149999999998</v>
       </c>
       <c r="L11">
         <f t="shared" si="5"/>
-        <v>7.0010616100275209</v>
+        <v>7.4389046002833874</v>
       </c>
       <c r="M11">
         <f t="shared" si="2"/>
-        <v>0.76705597416577009</v>
+        <v>0.46474345549738044</v>
       </c>
       <c r="N11">
         <f t="shared" si="3"/>
-        <v>2.0702290076335901</v>
+        <v>2.7695219123505979</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>1.2767415593535636</v>
+        <v>2.2426672947052388</v>
       </c>
       <c r="P11">
         <f t="shared" si="1"/>
-        <v>87.239426523297482</v>
+        <v>87.804029304029314</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1117,57 +1117,57 @@
         <v>60</v>
       </c>
       <c r="B12">
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="C12">
         <f t="shared" si="4"/>
-        <v>56.4</v>
+        <v>55.2</v>
       </c>
       <c r="D12">
-        <v>18.940000000000001</v>
+        <v>19.54</v>
       </c>
       <c r="E12">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="F12">
         <f>D12*E12</f>
-        <v>49.244000000000007</v>
+        <v>48.459199999999996</v>
       </c>
       <c r="G12">
         <f t="shared" si="9"/>
-        <v>7.2846153846153845</v>
+        <v>7.879032258064516</v>
       </c>
       <c r="H12">
-        <v>22.533628</v>
+        <v>23.427247999999999</v>
       </c>
       <c r="I12">
-        <v>3.0747490000000002</v>
+        <v>2.9393820000000002</v>
       </c>
       <c r="J12">
-        <v>19.081296999999999</v>
+        <v>19.602093</v>
       </c>
       <c r="K12">
-        <v>2.6036730000000001</v>
+        <v>2.4594450000000001</v>
       </c>
       <c r="L12">
         <f t="shared" si="5"/>
-        <v>7.3286073174319499</v>
+        <v>7.9701286265803866</v>
       </c>
       <c r="M12">
         <f t="shared" si="2"/>
-        <v>0.74602428722279834</v>
+        <v>0.31777379733879657</v>
       </c>
       <c r="N12">
         <f t="shared" si="3"/>
-        <v>0.1412692307692322</v>
+        <v>0.82883064516128557</v>
       </c>
       <c r="O12">
         <f t="shared" si="0"/>
-        <v>0.60390192884408733</v>
+        <v>1.1561872769670367</v>
       </c>
       <c r="P12">
         <f t="shared" si="1"/>
-        <v>87.312056737588662</v>
+        <v>87.788405797101433</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1175,57 +1175,57 @@
         <v>60</v>
       </c>
       <c r="B13">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="C13">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>52.2</v>
       </c>
       <c r="D13">
-        <v>19.41</v>
+        <v>19.91</v>
       </c>
       <c r="E13">
-        <v>2.42</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F13">
         <f t="shared" ref="F13:F14" si="12">D13*E13</f>
-        <v>46.972200000000001</v>
+        <v>44.996599999999994</v>
       </c>
       <c r="G13">
         <f>D13/E13</f>
-        <v>8.0206611570247937</v>
+        <v>8.8097345132743374</v>
       </c>
       <c r="H13">
-        <v>22.533055999999998</v>
+        <v>23.426811000000001</v>
       </c>
       <c r="I13">
-        <v>2.8748619999999998</v>
+        <v>2.7394229999999999</v>
       </c>
       <c r="J13">
-        <v>19.507757000000002</v>
+        <v>19.970376999999999</v>
       </c>
       <c r="K13">
-        <v>2.4888819999999998</v>
+        <v>2.3352439999999999</v>
       </c>
       <c r="L13">
         <f t="shared" si="5"/>
-        <v>7.8379597747100922</v>
+        <v>8.5517303545154171</v>
       </c>
       <c r="M13">
         <f t="shared" si="2"/>
-        <v>0.50364245234415983</v>
+        <v>0.30324962330486699</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
-        <v>2.8463636363636318</v>
+        <v>3.3293805309734554</v>
       </c>
       <c r="O13">
         <f t="shared" si="0"/>
-        <v>2.277884313248725</v>
+        <v>2.9286258101213458</v>
       </c>
       <c r="P13">
         <f t="shared" si="1"/>
-        <v>86.985555555555564</v>
+        <v>86.200383141762444</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1233,57 +1233,57 @@
         <v>60</v>
       </c>
       <c r="B14">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="C14">
         <f t="shared" si="4"/>
-        <v>52.2</v>
+        <v>48.6</v>
       </c>
       <c r="D14">
-        <v>19.78</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="E14">
-        <v>2.29</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="F14">
         <f t="shared" si="12"/>
-        <v>45.296200000000006</v>
+        <v>41.819999999999993</v>
       </c>
       <c r="G14">
         <f>D14/E14</f>
-        <v>8.6375545851528379</v>
+        <v>9.9512195121951219</v>
       </c>
       <c r="H14">
-        <v>22.535361999999999</v>
+        <v>23.426421999999999</v>
       </c>
       <c r="I14">
-        <v>2.6735730000000002</v>
+        <v>2.4182959999999998</v>
       </c>
       <c r="J14">
-        <v>19.885262999999998</v>
+        <v>20.420041999999999</v>
       </c>
       <c r="K14">
-        <v>2.3591679999999999</v>
+        <v>2.1079490000000001</v>
       </c>
       <c r="L14">
         <f t="shared" si="5"/>
-        <v>8.428930453447995</v>
+        <v>9.6871613117774658</v>
       </c>
       <c r="M14">
         <f t="shared" si="2"/>
-        <v>0.53216885743173514</v>
+        <v>9.8245098039216258E-2</v>
       </c>
       <c r="N14">
         <f t="shared" si="3"/>
-        <v>3.0204366812227028</v>
+        <v>2.8267804878048906</v>
       </c>
       <c r="O14">
         <f t="shared" si="0"/>
-        <v>2.415314770495907</v>
+        <v>2.6535260336087996</v>
       </c>
       <c r="P14">
         <f t="shared" si="1"/>
-        <v>86.774329501915716</v>
+        <v>86.049382716049365</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1291,57 +1291,57 @@
         <v>60</v>
       </c>
       <c r="B15">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="C15">
         <f t="shared" si="4"/>
-        <v>47.400000000000006</v>
+        <v>44.4</v>
       </c>
       <c r="D15">
-        <v>20.309999999999999</v>
+        <v>20.77</v>
       </c>
       <c r="E15">
-        <v>2.0099999999999998</v>
+        <v>1.86</v>
       </c>
       <c r="F15">
         <f t="shared" ref="F15" si="13">D15*E15</f>
-        <v>40.823099999999997</v>
+        <v>38.632200000000005</v>
       </c>
       <c r="G15">
         <f>D15/E15</f>
-        <v>10.104477611940299</v>
+        <v>11.166666666666666</v>
       </c>
       <c r="H15">
-        <v>22.533543000000002</v>
+        <v>23.429234000000001</v>
       </c>
       <c r="I15">
-        <v>2.3436949999999999</v>
+        <v>2.159837</v>
       </c>
       <c r="J15">
-        <v>20.378786000000002</v>
+        <v>20.759868999999998</v>
       </c>
       <c r="K15">
-        <v>2.11958</v>
+        <v>1.9137599999999999</v>
       </c>
       <c r="L15">
         <f t="shared" si="5"/>
-        <v>9.6145396729540771</v>
+        <v>10.847686752779868</v>
       </c>
       <c r="M15">
         <f t="shared" si="2"/>
-        <v>0.33868045297884247</v>
+        <v>4.8777082330289948E-2</v>
       </c>
       <c r="N15">
         <f t="shared" si="3"/>
-        <v>5.4517412935323506</v>
+        <v>2.8903225806451509</v>
       </c>
       <c r="O15">
         <f t="shared" si="0"/>
-        <v>4.8487211096125318</v>
+        <v>2.8565365422698323</v>
       </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>86.124683544303778</v>
+        <v>87.009459459459464</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1349,57 +1349,57 @@
         <v>60</v>
       </c>
       <c r="B16">
-        <v>0.75</v>
+        <v>0.54</v>
       </c>
       <c r="C16">
         <f t="shared" si="4"/>
-        <v>45</v>
+        <v>32.400000000000006</v>
       </c>
       <c r="D16">
-        <v>20.62</v>
+        <v>21.31</v>
       </c>
       <c r="E16">
-        <v>1.87</v>
+        <v>1.27</v>
       </c>
       <c r="F16">
         <f>D16*E16</f>
-        <v>38.559400000000004</v>
+        <v>27.063699999999997</v>
       </c>
       <c r="G16">
         <f t="shared" ref="G16:G18" si="14">D16/E16</f>
-        <v>11.026737967914439</v>
+        <v>16.779527559055119</v>
       </c>
       <c r="H16">
-        <v>22.535171999999999</v>
+        <v>23.437695000000001</v>
       </c>
       <c r="I16">
-        <v>2.1489539999999998</v>
+        <v>1.5582389999999999</v>
       </c>
       <c r="J16">
-        <v>20.665606</v>
+        <v>21.242069000000001</v>
       </c>
       <c r="K16">
-        <v>1.970672</v>
+        <v>1.4122650000000001</v>
       </c>
       <c r="L16">
         <f t="shared" ref="L16:L18" si="15">J16/K16</f>
-        <v>10.486578182467706</v>
+        <v>15.041135339330792</v>
       </c>
       <c r="M16">
         <f t="shared" si="2"/>
-        <v>0.22117361784674766</v>
+        <v>0.3187752229000374</v>
       </c>
       <c r="N16">
         <f t="shared" si="3"/>
-        <v>5.383529411764699</v>
+        <v>11.201968503937014</v>
       </c>
       <c r="O16">
         <f t="shared" si="0"/>
-        <v>4.8986362695702708</v>
+        <v>10.360197649225224</v>
       </c>
       <c r="P16">
         <f t="shared" si="1"/>
-        <v>85.687555555555562</v>
+        <v>83.529938271604919</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1407,57 +1407,57 @@
         <v>60</v>
       </c>
       <c r="B17">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="C17">
         <f t="shared" ref="C17:C18" si="16">A15*B17</f>
-        <v>26.4</v>
+        <v>15</v>
       </c>
       <c r="D17">
-        <v>21.49</v>
+        <v>22.11</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.42</v>
       </c>
       <c r="F17">
         <f t="shared" ref="F17:F18" si="17">D17*E17</f>
-        <v>21.49</v>
+        <v>9.2861999999999991</v>
       </c>
       <c r="G17">
         <f t="shared" si="14"/>
-        <v>21.49</v>
+        <v>52.642857142857146</v>
       </c>
       <c r="H17">
-        <v>22.548850999999999</v>
+        <v>23.447426</v>
       </c>
       <c r="I17">
-        <v>1.2683180000000001</v>
+        <v>0.68671599999999999</v>
       </c>
       <c r="J17">
-        <v>21.433184000000001</v>
+        <v>21.980999000000001</v>
       </c>
       <c r="K17">
-        <v>1.2055640000000001</v>
+        <v>0.64376800000000001</v>
       </c>
       <c r="L17">
         <f t="shared" si="15"/>
-        <v>17.778553440547327</v>
+        <v>34.144286451019624</v>
       </c>
       <c r="M17">
         <f t="shared" si="2"/>
-        <v>0.26438343415541071</v>
+        <v>0.5834509271822651</v>
       </c>
       <c r="N17">
         <f t="shared" si="3"/>
-        <v>20.556400000000007</v>
+        <v>53.278095238095247</v>
       </c>
       <c r="O17">
         <f t="shared" si="0"/>
-        <v>17.270574962553148</v>
+        <v>35.139754367126905</v>
       </c>
       <c r="P17">
         <f t="shared" si="1"/>
-        <v>81.401515151515142</v>
+        <v>61.907999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1472,50 +1472,50 @@
         <v>7.1999999999999993</v>
       </c>
       <c r="D18">
-        <v>22.3</v>
+        <v>22.51</v>
       </c>
       <c r="E18">
         <v>0.05</v>
       </c>
       <c r="F18">
         <f t="shared" si="17"/>
-        <v>1.115</v>
+        <v>1.1255000000000002</v>
       </c>
       <c r="G18">
         <f t="shared" si="14"/>
-        <v>446</v>
+        <v>450.2</v>
       </c>
       <c r="H18">
-        <v>22.826053999999999</v>
+        <v>23.450655000000001</v>
       </c>
       <c r="I18">
-        <v>0.47076800000000002</v>
+        <v>0.30788100000000002</v>
       </c>
       <c r="J18">
-        <v>22.157703000000001</v>
+        <v>22.318256000000002</v>
       </c>
       <c r="K18">
-        <v>0.45698299999999997</v>
+        <v>0.293014</v>
       </c>
       <c r="L18">
         <f t="shared" si="15"/>
-        <v>48.486930586039314</v>
+        <v>76.167882763280943</v>
       </c>
       <c r="M18">
         <f t="shared" si="2"/>
-        <v>0.63810313901344951</v>
+        <v>0.85181697023545055</v>
       </c>
       <c r="N18">
         <f t="shared" si="3"/>
-        <v>813.96599999999989</v>
+        <v>486.02799999999996</v>
       </c>
       <c r="O18">
         <f t="shared" si="0"/>
-        <v>89.128490899991192</v>
+        <v>83.081323242274323</v>
       </c>
       <c r="P18">
         <f t="shared" si="1"/>
-        <v>15.486111111111111</v>
+        <v>15.631944444444448</v>
       </c>
     </row>
   </sheetData>
